--- a/acc-v3.xlsx
+++ b/acc-v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13584"/>
+    <workbookView windowWidth="30720" windowHeight="13464"/>
   </bookViews>
   <sheets>
     <sheet name="acc-v3" sheetId="1" r:id="rId1"/>
@@ -148,10 +148,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -162,6 +162,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -169,8 +177,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,7 +223,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -222,9 +275,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,46 +284,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,26 +298,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -315,19 +315,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,13 +435,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,139 +489,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,11 +509,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,21 +529,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,21 +544,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -592,16 +568,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -611,148 +611,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1574,35 +1574,35 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.41403088</v>
+        <v>0.40600583</v>
       </c>
       <c r="C8">
-        <v>0.5795505</v>
+        <v>0.56835645</v>
       </c>
       <c r="D8">
-        <v>0.39698857</v>
+        <v>0.37917387</v>
       </c>
       <c r="E8">
-        <v>0.39275324</v>
+        <v>0.37505326</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="1">
         <f>AVERAGE(B8:B10)*100</f>
-        <v>41.476333</v>
+        <v>40.138202</v>
       </c>
       <c r="I8" s="1">
         <f>AVERAGE(C8:C10)*100</f>
-        <v>58.9376963333333</v>
+        <v>57.9925713333333</v>
       </c>
       <c r="J8" s="1">
         <f>AVERAGE(D8:D10)*100</f>
-        <v>39.3993836666667</v>
+        <v>37.5730713333333</v>
       </c>
       <c r="K8" s="1">
         <f>AVERAGE(E8:E10)*100</f>
-        <v>38.9956383333333</v>
+        <v>37.1689093333333</v>
       </c>
       <c r="M8" t="str">
         <f>LEFT(A8,LEN(A8)-3)</f>
@@ -1610,19 +1610,19 @@
       </c>
       <c r="N8" t="str">
         <f>TEXT(H8,"0.0")&amp;"±"&amp;TEXT(H9,"0.0")</f>
-        <v>41.5±0.1</v>
+        <v>40.1±0.4</v>
       </c>
       <c r="O8" t="str">
         <f>TEXT(I8,"0.0")&amp;"±"&amp;TEXT(I9,"0.0")</f>
-        <v>58.9±0.9</v>
+        <v>58.0±1.0</v>
       </c>
       <c r="P8" t="str">
         <f>TEXT(J8,"0.0")&amp;"±"&amp;TEXT(J9,"0.0")</f>
-        <v>39.4±0.4</v>
+        <v>37.6±0.4</v>
       </c>
       <c r="Q8" t="str">
         <f>TEXT(K8,"0.0")&amp;"±"&amp;TEXT(K9,"0.0")</f>
-        <v>39.0±0.4</v>
+        <v>37.2±0.4</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1630,35 +1630,35 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.41583082</v>
+        <v>0.3997601</v>
       </c>
       <c r="C9">
-        <v>0.59201437</v>
+        <v>0.58315438</v>
       </c>
       <c r="D9">
-        <v>0.38984907</v>
+        <v>0.37179554</v>
       </c>
       <c r="E9">
-        <v>0.38579419</v>
+        <v>0.36723927</v>
       </c>
       <c r="G9" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="1">
         <f>STDEV(B8:B10)*100</f>
-        <v>0.0945587040996229</v>
+        <v>0.406334757155969</v>
       </c>
       <c r="I9" s="1">
         <f>STDEV(C8:C10)*100</f>
-        <v>0.880902467141703</v>
+        <v>1.03401570412752</v>
       </c>
       <c r="J9" s="1">
         <f>STDEV(D8:D10)*100</f>
-        <v>0.370608250897538</v>
+        <v>0.371369071106272</v>
       </c>
       <c r="K9" s="1">
         <f>STDEV(E8:E10)*100</f>
-        <v>0.367494250099691</v>
+        <v>0.401853178765993</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1666,16 +1666,16 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.41442829</v>
+        <v>0.39838013</v>
       </c>
       <c r="C10">
-        <v>0.59656602</v>
+        <v>0.58826631</v>
       </c>
       <c r="D10">
-        <v>0.39514387</v>
+        <v>0.37622273</v>
       </c>
       <c r="E10">
-        <v>0.39132172</v>
+        <v>0.37277475</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1913,35 +1913,35 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.4658044</v>
+        <v>0.45906022</v>
       </c>
       <c r="C17">
-        <v>0.59072882</v>
+        <v>0.5797838</v>
       </c>
       <c r="D17">
-        <v>0.41336206</v>
+        <v>0.39064643</v>
       </c>
       <c r="E17">
-        <v>0.40536544</v>
+        <v>0.38312489</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="1">
         <f>AVERAGE(B17:B19)*100</f>
-        <v>46.7996856666667</v>
+        <v>45.9905503333333</v>
       </c>
       <c r="I17" s="1">
         <f>AVERAGE(C17:C19)*100</f>
-        <v>60.7053756666667</v>
+        <v>60.36162</v>
       </c>
       <c r="J17" s="1">
         <f>AVERAGE(D17:D19)*100</f>
-        <v>41.5249346666667</v>
+        <v>39.4454896666667</v>
       </c>
       <c r="K17" s="1">
         <f>AVERAGE(E17:E19)*100</f>
-        <v>40.6493873333333</v>
+        <v>38.5068726666667</v>
       </c>
       <c r="M17" t="str">
         <f>LEFT(A17,LEN(A17)-3)</f>
@@ -1949,19 +1949,19 @@
       </c>
       <c r="N17" t="str">
         <f>TEXT(H17,"0.0")&amp;"±"&amp;TEXT(H18,"0.0")</f>
-        <v>46.8±0.7</v>
+        <v>46.0±0.7</v>
       </c>
       <c r="O17" t="str">
         <f>TEXT(I17,"0.0")&amp;"±"&amp;TEXT(I18,"0.0")</f>
-        <v>60.7±1.7</v>
+        <v>60.4±2.3</v>
       </c>
       <c r="P17" t="str">
         <f>TEXT(J17,"0.0")&amp;"±"&amp;TEXT(J18,"0.0")</f>
-        <v>41.5±0.2</v>
+        <v>39.4±0.3</v>
       </c>
       <c r="Q17" t="str">
         <f>TEXT(K17,"0.0")&amp;"±"&amp;TEXT(K18,"0.0")</f>
-        <v>40.6±0.1</v>
+        <v>38.5±0.2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1969,35 +1969,35 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>0.46185672</v>
+        <v>0.4529669</v>
       </c>
       <c r="C18">
-        <v>0.62396842</v>
+        <v>0.62657851</v>
       </c>
       <c r="D18">
-        <v>0.41616219</v>
+        <v>0.39541903</v>
       </c>
       <c r="E18">
-        <v>0.40723583</v>
+        <v>0.38512993</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
       </c>
       <c r="H18" s="1">
         <f>STDEV(B17:B19)*100</f>
-        <v>0.748131860634429</v>
+        <v>0.739755404746955</v>
       </c>
       <c r="I18" s="1">
         <f>STDEV(C17:C19)*100</f>
-        <v>1.66276452089895</v>
+        <v>2.34094855443707</v>
       </c>
       <c r="J18" s="1">
         <f>STDEV(D17:D19)*100</f>
-        <v>0.163472837549036</v>
+        <v>0.342959207098066</v>
       </c>
       <c r="K18" s="1">
         <f>STDEV(E17:E19)*100</f>
-        <v>0.0993283871022441</v>
+        <v>0.191396905702088</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2005,16 +2005,16 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>0.47632945</v>
+        <v>0.46768939</v>
       </c>
       <c r="C19">
-        <v>0.60646403</v>
+        <v>0.60448629</v>
       </c>
       <c r="D19">
-        <v>0.41622379</v>
+        <v>0.39729923</v>
       </c>
       <c r="E19">
-        <v>0.40688035</v>
+        <v>0.38695136</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -2252,35 +2252,35 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>0.37501428</v>
+        <v>0.36545831</v>
       </c>
       <c r="C26">
-        <v>0.50094569</v>
+        <v>0.50128973</v>
       </c>
       <c r="D26">
-        <v>0.34261894</v>
+        <v>0.32855597</v>
       </c>
       <c r="E26">
-        <v>0.34105724</v>
+        <v>0.32714266</v>
       </c>
       <c r="G26" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="1">
         <f>AVERAGE(B26:B28)*100</f>
-        <v>38.1467146666667</v>
+        <v>37.1572296666667</v>
       </c>
       <c r="I26" s="1">
         <f>AVERAGE(C26:C28)*100</f>
-        <v>48.8429656666667</v>
+        <v>49.3538896666667</v>
       </c>
       <c r="J26" s="1">
         <f>AVERAGE(D26:D28)*100</f>
-        <v>34.5175613333333</v>
+        <v>32.9617946666667</v>
       </c>
       <c r="K26" s="1">
         <f>AVERAGE(E26:E28)*100</f>
-        <v>34.3572813333333</v>
+        <v>32.7943943333333</v>
       </c>
       <c r="M26" t="str">
         <f>LEFT(A26,LEN(A26)-3)</f>
@@ -2288,19 +2288,19 @@
       </c>
       <c r="N26" t="str">
         <f>TEXT(H26,"0.0")&amp;"±"&amp;TEXT(H27,"0.0")</f>
-        <v>38.1±0.7</v>
+        <v>37.2±0.6</v>
       </c>
       <c r="O26" t="str">
         <f>TEXT(I26,"0.0")&amp;"±"&amp;TEXT(I27,"0.0")</f>
-        <v>48.8±1.5</v>
+        <v>49.4±1.1</v>
       </c>
       <c r="P26" t="str">
         <f>TEXT(J26,"0.0")&amp;"±"&amp;TEXT(J27,"0.0")</f>
-        <v>34.5±0.3</v>
+        <v>33.0±0.2</v>
       </c>
       <c r="Q26" t="str">
         <f>TEXT(K26,"0.0")&amp;"±"&amp;TEXT(K27,"0.0")</f>
-        <v>34.4±0.2</v>
+        <v>32.8±0.1</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2308,35 +2308,35 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>0.37974456</v>
+        <v>0.37143466</v>
       </c>
       <c r="C27">
-        <v>0.49219972</v>
+        <v>0.49808535</v>
       </c>
       <c r="D27">
-        <v>0.34771276</v>
+        <v>0.3315967</v>
       </c>
       <c r="E27">
-        <v>0.34580269</v>
+        <v>0.32954684</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
       </c>
       <c r="H27" s="1">
         <f>STDEV(B26:B28)*100</f>
-        <v>0.746474481303504</v>
+        <v>0.618395387733715</v>
       </c>
       <c r="I27" s="1">
         <f>STDEV(C26:C28)*100</f>
-        <v>1.47665400919522</v>
+        <v>1.07696080391876</v>
       </c>
       <c r="J27" s="1">
         <f>STDEV(D26:D28)*100</f>
-        <v>0.25469661395734</v>
+        <v>0.171518783975208</v>
       </c>
       <c r="K27" s="1">
         <f>STDEV(E26:E28)*100</f>
-        <v>0.238559025497537</v>
+        <v>0.138814924278097</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2344,16 +2344,16 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>0.3896426</v>
+        <v>0.37782392</v>
       </c>
       <c r="C28">
-        <v>0.47214356</v>
+        <v>0.48124161</v>
       </c>
       <c r="D28">
-        <v>0.34519514</v>
+        <v>0.32870117</v>
       </c>
       <c r="E28">
-        <v>0.34385851</v>
+        <v>0.32714233</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2591,35 +2591,35 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>0.35010567</v>
+        <v>0.34372133</v>
       </c>
       <c r="C35">
-        <v>0.48927569</v>
+        <v>0.48937181</v>
       </c>
       <c r="D35">
-        <v>0.31390992</v>
+        <v>0.30102709</v>
       </c>
       <c r="E35">
-        <v>0.31177223</v>
+        <v>0.29898629</v>
       </c>
       <c r="G35" t="s">
         <v>5</v>
       </c>
       <c r="H35" s="1">
         <f>AVERAGE(B35:B37)*100</f>
-        <v>34.4168113333333</v>
+        <v>33.776003</v>
       </c>
       <c r="I35" s="1">
         <f>AVERAGE(C35:C37)*100</f>
-        <v>48.863385</v>
+        <v>49.1511176666667</v>
       </c>
       <c r="J35" s="1">
         <f>AVERAGE(D35:D37)*100</f>
-        <v>31.0976613333333</v>
+        <v>29.8687716666667</v>
       </c>
       <c r="K35" s="1">
         <f>AVERAGE(E35:E37)*100</f>
-        <v>30.9042116666667</v>
+        <v>29.6864153333333</v>
       </c>
       <c r="M35" t="str">
         <f>LEFT(A35,LEN(A35)-3)</f>
@@ -2627,19 +2627,19 @@
       </c>
       <c r="N35" t="str">
         <f>TEXT(H35,"0.0")&amp;"±"&amp;TEXT(H36,"0.0")</f>
-        <v>34.4±0.6</v>
+        <v>33.8±0.7</v>
       </c>
       <c r="O35" t="str">
         <f>TEXT(I35,"0.0")&amp;"±"&amp;TEXT(I36,"0.0")</f>
-        <v>48.9±0.6</v>
+        <v>49.2±0.5</v>
       </c>
       <c r="P35" t="str">
         <f>TEXT(J35,"0.0")&amp;"±"&amp;TEXT(J36,"0.0")</f>
-        <v>31.1±0.3</v>
+        <v>29.9±0.4</v>
       </c>
       <c r="Q35" t="str">
         <f>TEXT(K35,"0.0")&amp;"±"&amp;TEXT(K36,"0.0")</f>
-        <v>30.9±0.3</v>
+        <v>29.7±0.4</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2647,35 +2647,35 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>0.33766913</v>
+        <v>0.33024633</v>
       </c>
       <c r="C36">
-        <v>0.49422005</v>
+        <v>0.49685082</v>
       </c>
       <c r="D36">
-        <v>0.30714753</v>
+        <v>0.29418829</v>
       </c>
       <c r="E36">
-        <v>0.30523941</v>
+        <v>0.29235312</v>
       </c>
       <c r="G36" t="s">
         <v>7</v>
       </c>
       <c r="H36" s="1">
         <f>STDEV(B35:B37)*100</f>
-        <v>0.623724953159911</v>
+        <v>0.687032499740734</v>
       </c>
       <c r="I36" s="1">
         <f>STDEV(C35:C37)*100</f>
-        <v>0.593321461213061</v>
+        <v>0.465459189429465</v>
       </c>
       <c r="J36" s="1">
         <f>STDEV(D35:D37)*100</f>
-        <v>0.346904763666245</v>
+        <v>0.389764918407664</v>
       </c>
       <c r="K36" s="1">
         <f>STDEV(E35:E37)*100</f>
-        <v>0.339592058684142</v>
+        <v>0.390894570507615</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2683,16 +2683,16 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>0.34472954</v>
+        <v>0.33931243</v>
       </c>
       <c r="C37">
-        <v>0.48240581</v>
+        <v>0.4883109</v>
       </c>
       <c r="D37">
-        <v>0.31187239</v>
+        <v>0.30084777</v>
       </c>
       <c r="E37">
-        <v>0.31011471</v>
+        <v>0.29925305</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>

--- a/acc-v3.xlsx
+++ b/acc-v3.xlsx
@@ -147,10 +147,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="0.0_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -170,33 +170,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -224,7 +202,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,21 +216,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -276,7 +255,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,25 +263,46 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -315,187 +315,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,21 +506,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -533,46 +518,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,147 +556,197 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -760,7 +760,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1302,7 +1302,7 @@
     <col min="1" max="1" width="27.1296296296296" customWidth="1"/>
     <col min="2" max="5" width="11.5"/>
     <col min="8" max="11" width="12.6296296296296"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="13" max="13" width="21.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17">
